--- a/data/trans_bre/P19C07-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C07-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,97</t>
+          <t>-2,55; 4,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,37</t>
+          <t>-4,17; 3,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 5,7</t>
+          <t>-1,06; 6,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 6,7</t>
+          <t>-6,07; 6,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,88; 124,63</t>
+          <t>-33,83; 114,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 64,78</t>
+          <t>-39,72; 57,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 147,55</t>
+          <t>-15,57; 159,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,65; 193,16</t>
+          <t>-58,24; 209,15</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,54</t>
+          <t>-2,51; 2,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,04</t>
+          <t>-1,45; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,59</t>
+          <t>-0,49; 4,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,9</t>
+          <t>-2,21; 6,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,65; 93,6</t>
+          <t>-49,33; 94,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 123,72</t>
+          <t>-27,96; 116,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 183,72</t>
+          <t>-13,04; 194,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 171,11</t>
+          <t>-31,37; 190,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,39</t>
+          <t>-1,06; 2,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,53</t>
+          <t>-1,23; 2,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,16</t>
+          <t>-2,99; 0,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,79</t>
+          <t>-1,74; 2,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 183,09</t>
+          <t>-41,04; 216,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 146,68</t>
+          <t>-35,82; 143,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 58,48</t>
+          <t>-67,26; 47,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 121,92</t>
+          <t>-35,84; 136,59</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,76</t>
+          <t>-3,86; 0,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,96</t>
+          <t>-1,78; 2,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,08</t>
+          <t>-0,45; 3,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,11</t>
+          <t>-0,76; 3,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,67; 39,74</t>
+          <t>-75,71; 39,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,19; 186,34</t>
+          <t>-62,49; 223,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 298,16</t>
+          <t>-29,59; 343,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 291,75</t>
+          <t>-22,33; 279,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,75</t>
+          <t>-1,47; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,76</t>
+          <t>-1,89; 1,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,17</t>
+          <t>-1,71; 2,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,81</t>
+          <t>-0,02; 2,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,93; 570,42</t>
+          <t>-68,73; 675,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 448,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 317,71</t>
+          <t>-78,68; 411,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 412,5</t>
+          <t>-9,05; 456,83</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 2,04</t>
+          <t>-4,52; 2,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,13</t>
+          <t>-0,81; 3,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,58</t>
+          <t>-1,67; 3,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,82</t>
+          <t>-3,29; 0,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 86,02</t>
+          <t>-71,09; 85,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,36; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-67,48; 839,68</t>
+          <t>-70,09; 696,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-86,27; 44,87</t>
+          <t>-83,56; 46,81</t>
         </is>
       </c>
     </row>
@@ -1260,32 +1260,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,2</t>
+          <t>-3,56; 2,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,49</t>
+          <t>-4,08; 1,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,25</t>
+          <t>-0,52; 4,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,11</t>
+          <t>-1,75; 2,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 671,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-92,25; 257,76</t>
+          <t>-89,72; 314,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 214,75</t>
+          <t>-49,65; 273,5</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,0</t>
+          <t>-0,96; 1,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,21</t>
+          <t>-0,7; 1,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,65</t>
+          <t>-0,13; 1,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,86</t>
+          <t>-0,65; 1,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 33,87</t>
+          <t>-24,1; 36,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 43,33</t>
+          <t>-19,19; 41,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 67,6</t>
+          <t>-3,05; 71,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 70,99</t>
+          <t>-15,71; 67,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C07-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C07-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,85</t>
+          <t>-1,88; 4,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,82</t>
+          <t>-4,15; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 6,01</t>
+          <t>-1,09; 6,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 6,56</t>
+          <t>-5,94; 6,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 114,28</t>
+          <t>-27,98; 122,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 57,66</t>
+          <t>-38,41; 62,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 159,0</t>
+          <t>-17,28; 158,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,24; 209,15</t>
+          <t>-58,28; 142,24</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,51</t>
+          <t>-2,41; 2,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,95</t>
+          <t>-1,59; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,7</t>
+          <t>-0,71; 4,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 6,26</t>
+          <t>-1,52; 6,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,33; 94,89</t>
+          <t>-49,3; 92,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 116,39</t>
+          <t>-31,27; 111,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 194,5</t>
+          <t>-17,45; 171,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 190,25</t>
+          <t>-21,38; 175,23</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,73</t>
+          <t>-1,26; 2,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,4</t>
+          <t>-1,36; 2,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,98</t>
+          <t>-2,89; 1,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,87</t>
+          <t>-1,46; 2,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 216,11</t>
+          <t>-42,62; 199,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 143,19</t>
+          <t>-41,05; 154,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-67,26; 47,99</t>
+          <t>-64,67; 71,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 136,59</t>
+          <t>-33,18; 138,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,87</t>
+          <t>-3,85; 0,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,11</t>
+          <t>-1,89; 2,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,25</t>
+          <t>-0,75; 3,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,13</t>
+          <t>-1,84; 1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 39,33</t>
+          <t>-75,68; 47,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,49; 223,25</t>
+          <t>-62,33; 208,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 343,84</t>
+          <t>-36,29; 345,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 279,31</t>
+          <t>-40,32; 77,84</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>105,81%</t>
+          <t>125,19%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,69</t>
+          <t>-1,43; 2,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,55</t>
+          <t>-1,96; 1,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,42</t>
+          <t>-1,67; 2,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,74</t>
+          <t>0,1; 3,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,73; 675,52</t>
+          <t>-75,14; 572,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 448,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-78,68; 411,87</t>
+          <t>-70,82; 390,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 456,83</t>
+          <t>0,08; 448,99</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-32,38%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 2,09</t>
+          <t>-4,86; 2,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,43</t>
+          <t>-0,57; 3,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,39</t>
+          <t>-1,63; 3,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,87</t>
+          <t>-1,72; 1,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 85,8</t>
+          <t>-75,14; 120,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,09; 696,47</t>
+          <t>-76,64; 666,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,56; 46,81</t>
+          <t>-51,42; 124,44</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 2,99</t>
+          <t>-3,3; 3,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,49</t>
+          <t>-3,71; 1,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,02</t>
+          <t>-0,5; 4,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,12</t>
+          <t>-1,76; 2,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-89,72; 314,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-49,65; 273,5</t>
+          <t>-52,96; 212,07</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,07</t>
+          <t>-0,98; 1,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,21</t>
+          <t>-0,74; 1,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,66</t>
+          <t>-0,29; 1,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,79</t>
+          <t>-0,34; 1,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 36,01</t>
+          <t>-24,35; 39,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 41,98</t>
+          <t>-19,52; 41,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 71,44</t>
+          <t>-8,54; 68,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 67,38</t>
+          <t>-8,2; 59,2</t>
         </is>
       </c>
     </row>
